--- a/docs/webbrain-tool-tiers.xlsx
+++ b/docs/webbrain-tool-tiers.xlsx
@@ -1869,14 +1869,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>Chrome</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>Chrome</t>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
